--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484530_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484530_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4115</v>
+        <v>5.7054</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7276</v>
+        <v>4.2196</v>
       </c>
       <c r="F2" t="n">
-        <v>1.684</v>
+        <v>1.4858</v>
       </c>
       <c r="G2" t="n">
         <v>5.4984</v>
@@ -610,13 +610,13 @@
         <v>0.733</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0964</v>
+        <v>0.3903</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6946</v>
+        <v>0.1867</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4018</v>
+        <v>0.2036</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. POVEDA CASTELLO</t>
+          <t>F. FERRER I SEGURA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2116</v>
+        <v>4.119</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8722</v>
+        <v>1.7125</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3394</v>
+        <v>2.4065</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7373</v>
+        <v>4.4499</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8494</v>
+        <v>2.8246</v>
       </c>
       <c r="I3" t="n">
-        <v>2.888</v>
+        <v>1.6253</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0079</v>
+        <v>3.6519</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0492</v>
+        <v>2.8919</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9587</v>
+        <v>0.76</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2706</v>
+        <v>0.798</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1999</v>
+        <v>-0.0673</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9293</v>
+        <v>0.8653</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8326</v>
+        <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1627</v>
+        <v>0.4859</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9366</v>
+        <v>0.2048</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0994</v>
+        <v>0.2811</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3115</v>
+        <v>-0.6335</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6335</v>
+        <v>-0.3115</v>
       </c>
       <c r="X3" t="n">
         <v>-0.3219</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. FERRER I SEGURA</t>
+          <t>M. POVEDA CASTELLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5034</v>
+        <v>4.013</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1216</v>
+        <v>2.1196</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3817</v>
+        <v>1.8935</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4499</v>
+        <v>3.7373</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8246</v>
+        <v>0.8494</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6253</v>
+        <v>2.888</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6519</v>
+        <v>4.0079</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8919</v>
+        <v>2.0492</v>
       </c>
       <c r="L4" t="n">
-        <v>0.76</v>
+        <v>1.9587</v>
       </c>
       <c r="M4" t="n">
-        <v>0.798</v>
+        <v>-0.2706</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0673</v>
+        <v>-1.1999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8653</v>
+        <v>0.9293</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6493</v>
+        <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1298</v>
+        <v>-0.0358</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3861</v>
+        <v>-0.6893</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2563</v>
+        <v>0.6534</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6335</v>
+        <v>0.3115</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3115</v>
+        <v>0.6335</v>
       </c>
       <c r="X4" t="n">
         <v>-0.3219</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ NARRO</t>
+          <t>S. HERRANDO CUENCA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.193</v>
+        <v>2.3382</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5637</v>
+        <v>1.721</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6294</v>
+        <v>0.6172</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0713</v>
+        <v>0.8358</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2186</v>
+        <v>-0.8181</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1473</v>
+        <v>1.6539</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6127</v>
+        <v>1.3704</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5294</v>
+        <v>0.6778</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0833</v>
+        <v>0.6925</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.5345</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.748</v>
+        <v>-1.4959</v>
       </c>
       <c r="O5" t="n">
-        <v>0.064</v>
+        <v>0.9614</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9163</v>
+        <v>0.3665</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0261</v>
+        <v>-0.4531</v>
       </c>
       <c r="T5" t="n">
-        <v>1.629</v>
+        <v>-0.322</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3971</v>
+        <v>-0.1311</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3219</v>
+        <v>1.5889</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3219</v>
+        <v>1.5889</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. HERRANDO CUENCA</t>
+          <t>D. FERNANDEZ NARRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8183</v>
+        <v>2.1379</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4736</v>
+        <v>1.6572</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3447</v>
+        <v>0.4808</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8358</v>
+        <v>-0.0713</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8181</v>
+        <v>-0.2186</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6539</v>
+        <v>0.1473</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3704</v>
+        <v>0.6127</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6778</v>
+        <v>0.5294</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6925</v>
+        <v>0.0833</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5345</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4959</v>
+        <v>-0.748</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9614</v>
+        <v>0.064</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3665</v>
+        <v>0.9163</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9729</v>
+        <v>0.971</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5694</v>
+        <v>0.7225</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4036</v>
+        <v>0.2485</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5889</v>
+        <v>0.3219</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5889</v>
+        <v>0.3219</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3267</v>
+        <v>0.8273</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4609</v>
+        <v>-1.1585</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7876</v>
+        <v>1.9858</v>
       </c>
       <c r="G7" t="n">
         <v>0.9744</v>
@@ -1000,13 +1000,13 @@
         <v>1.8326</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9305</v>
+        <v>-0.4299</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7715</v>
+        <v>-0.4691</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.159</v>
+        <v>0.0392</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6335</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. FAJARDO PAÑOS</t>
+          <t>H. RUEDA RIOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3251</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3251</v>
+        <v>-0.5349</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.1876</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3251</v>
+        <v>-0.8756</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3251</v>
+        <v>0.6498</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-1.5254</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3251</v>
+        <v>-1.6507</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3251</v>
+        <v>0.1951</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.8458</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.7751</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.4548</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.3204</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.2613</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.1316</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.1297</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. CASASUS GOYENECHE</t>
+          <t>C. FAJARDO PAÑOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.067</v>
+        <v>0.3251</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2401</v>
+        <v>0.3251</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1731</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1387</v>
+        <v>0.3251</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3438</v>
+        <v>0.3251</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2051</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.235</v>
+        <v>0.3251</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5789</v>
+        <v>0.3251</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.814</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3738</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2351</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6089</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4176</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4751</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0575</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. RUEDA RIOS</t>
+          <t>G. CASASUS GOYENECHE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0373</v>
+        <v>0.2267</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1258</v>
+        <v>0.3502</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0885</v>
+        <v>-0.1236</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8756</v>
+        <v>0.1387</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6498</v>
+        <v>1.3438</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5254</v>
+        <v>-1.2051</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6507</v>
+        <v>-0.235</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1951</v>
+        <v>1.5789</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8458</v>
+        <v>-1.814</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7751</v>
+        <v>0.3738</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4548</v>
+        <v>-0.2351</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3204</v>
+        <v>0.6089</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9163</v>
+        <v>1.0995</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4287</v>
+        <v>0.5773</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4593</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0306</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>1.267</v>
+        <v>-1.5889</v>
       </c>
       <c r="W10" t="n">
-        <v>1.9005</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6335</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5426</v>
+        <v>-0.9102</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6421</v>
+        <v>-1.2575</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.3473</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3668</v>
@@ -1312,13 +1312,13 @@
         <v>2.0158</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6418</v>
+        <v>-0.0094</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4781</v>
+        <v>-0.0935</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1637</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6335</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2769</v>
+        <v>-3.6094</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9661</v>
+        <v>-4.1995</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6893</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2138</v>
@@ -1390,13 +1390,13 @@
         <v>1.4661</v>
       </c>
       <c r="S12" t="n">
-        <v>0.136</v>
+        <v>-0.1965</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0384</v>
+        <v>-0.2719</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1745</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.9998</v>
+        <v>15.8257</v>
       </c>
       <c r="E13" t="n">
-        <v>4.129</v>
+        <v>4.9548</v>
       </c>
       <c r="F13" t="n">
-        <v>10.871</v>
+        <v>10.8711</v>
       </c>
       <c r="G13" t="n">
         <v>12.4321</v>
       </c>
       <c r="H13" t="n">
-        <v>8.425400000000002</v>
+        <v>8.4254</v>
       </c>
       <c r="I13" t="n">
-        <v>4.006899999999999</v>
+        <v>4.006900000000001</v>
       </c>
       <c r="J13" t="n">
         <v>12.1147</v>
@@ -1456,7 +1456,7 @@
         <v>-6.7322</v>
       </c>
       <c r="O13" t="n">
-        <v>7.049900000000001</v>
+        <v>7.0499</v>
       </c>
       <c r="P13" t="n">
         <v>1.832399999999999</v>
@@ -1468,16 +1468,16 @@
         <v>13.7443</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7351000000000001</v>
+        <v>1.5611</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8406999999999998</v>
+        <v>-0.01500000000000007</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5759</v>
+        <v>1.576</v>
       </c>
       <c r="V13" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>-0.000100000000000211</v>
       </c>
       <c r="W13" t="n">
         <v>4.7668</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7092</v>
+        <v>5.2064</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1481</v>
+        <v>5.475</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4389</v>
+        <v>-0.2686</v>
       </c>
       <c r="G14" t="n">
         <v>2.493</v>
@@ -1546,13 +1546,13 @@
         <v>1.6493</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5565</v>
+        <v>1.0537</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.1671</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7163</v>
+        <v>0.8867</v>
       </c>
       <c r="V14" t="n">
         <v>0.0104</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. CORNEJO GONZALEZ</t>
+          <t>J. MARTINEZ TEJERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6281</v>
+        <v>1.6878</v>
       </c>
       <c r="E15" t="n">
-        <v>1.91</v>
+        <v>2.0525</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7181</v>
+        <v>-0.3647</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5238</v>
+        <v>0.5934</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7512</v>
+        <v>-1.4328</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2275</v>
+        <v>2.0261</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2901</v>
+        <v>2.146</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2227</v>
+        <v>0.1517</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0674</v>
+        <v>1.9943</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8139</v>
+        <v>-1.5526</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9739</v>
+        <v>-1.5845</v>
       </c>
       <c r="O15" t="n">
-        <v>0.16</v>
+        <v>0.0318</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3665</v>
+        <v>0.9163</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4634</v>
+        <v>0.1782</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2142</v>
+        <v>-0.0935</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2492</v>
+        <v>0.2717</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTINEZ TEJERO</t>
+          <t>M. CORNEJO GONZALEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3315</v>
+        <v>1.2543</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2833</v>
+        <v>0.2754</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9518</v>
+        <v>0.9789</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5934</v>
+        <v>-0.5238</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4328</v>
+        <v>-0.7512</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0261</v>
+        <v>0.2275</v>
       </c>
       <c r="J16" t="n">
-        <v>2.146</v>
+        <v>0.2901</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1517</v>
+        <v>0.2227</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9943</v>
+        <v>0.0674</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5526</v>
+        <v>-0.8139</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5845</v>
+        <v>-0.9739</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0318</v>
+        <v>0.16</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9163</v>
+        <v>0.3665</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1782</v>
+        <v>1.0896</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8627</v>
+        <v>0.5796</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3155</v>
+        <v>0.51</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MARTÍNEZ TEJERO</t>
+          <t>J. SOSA GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3251</v>
+        <v>1.0564</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3251</v>
+        <v>-0.7518</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.8082</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3251</v>
+        <v>1.3719</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3251</v>
+        <v>1.5675</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-0.1956</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3251</v>
+        <v>1.7874</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3251</v>
+        <v>2.9444</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-1.157</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-0.4155</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-1.3769</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.9614</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.1506</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.4238</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.5744</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SOSA GONZALEZ</t>
+          <t>J. MARTÍNEZ TEJERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5477</v>
+        <v>0.3251</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.521</v>
+        <v>0.3251</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9734</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3719</v>
+        <v>0.3251</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5675</v>
+        <v>0.3251</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1956</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7874</v>
+        <v>0.3251</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9444</v>
+        <v>0.3251</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.157</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4155</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3769</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9614</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4535</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.193</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2604</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2825</v>
+        <v>-1.1921</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6408</v>
+        <v>-3.0254</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3583</v>
+        <v>1.8333</v>
       </c>
       <c r="G19" t="n">
         <v>-3.6511</v>
@@ -1936,13 +1936,13 @@
         <v>1.0995</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0267</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0015</v>
+        <v>-0.3861</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0252</v>
+        <v>0.4498</v>
       </c>
       <c r="V19" t="n">
         <v>2.212</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7948</v>
+        <v>-1.5675</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4881</v>
+        <v>-2.8727</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6933</v>
+        <v>1.3053</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2817</v>
@@ -2014,13 +2014,13 @@
         <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3036</v>
+        <v>0.5309</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4012</v>
+        <v>0.0166</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.09760000000000001</v>
+        <v>0.5143</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4643</v>
+        <v>-2.1044</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3512</v>
+        <v>0.0334</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1131</v>
+        <v>-2.1378</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7042</v>
@@ -2092,13 +2092,13 @@
         <v>0.3665</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4931</v>
+        <v>-0.1333</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5505</v>
+        <v>-0.1659</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0574</v>
+        <v>0.0326</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6335</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. COMPANY LOPEZ</t>
+          <t>J. YUBERO OJEDA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7356</v>
+        <v>-2.8031</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9517</v>
+        <v>-3.0366</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7839</v>
+        <v>0.2335</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1127</v>
+        <v>-2.111</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2986</v>
+        <v>-1.0532</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8141</v>
+        <v>-1.0578</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0076</v>
+        <v>-1.0653</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5819</v>
+        <v>0.2167</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5895</v>
+        <v>-1.2821</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1051</v>
+        <v>-1.0457</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.8805</v>
+        <v>-1.27</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2246</v>
+        <v>0.2243</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4766</v>
+        <v>0.2242</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1116</v>
+        <v>-0.1387</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.3629</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. YUBERO OJEDA</t>
+          <t>A. COMPANY LOPEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3553</v>
+        <v>-2.9513</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6136</v>
+        <v>-2.0479</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2583</v>
+        <v>-0.9034</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.111</v>
+        <v>-2.1127</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0532</v>
+        <v>-1.2986</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0578</v>
+        <v>-0.8141</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0653</v>
+        <v>-0.0076</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2167</v>
+        <v>0.5819</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2821</v>
+        <v>-0.5895</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0457</v>
+        <v>-2.1051</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.27</v>
+        <v>-1.8805</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2243</v>
+        <v>-0.2246</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9163</v>
+        <v>0.733</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.328</v>
+        <v>0.2609</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7157</v>
+        <v>-0.2077</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3877</v>
+        <v>0.4687</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6056</v>
+        <v>-4.9719</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9095</v>
+        <v>-3.4287</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6962</v>
+        <v>-1.5432</v>
       </c>
       <c r="G24" t="n">
         <v>-3.329</v>
@@ -2326,13 +2326,13 @@
         <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8998</v>
+        <v>-0.266</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7157</v>
+        <v>-0.2349</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1841</v>
+        <v>-0.0311</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6439</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.2081</v>
+        <v>-5.7346</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0615</v>
+        <v>-3.8692</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1466</v>
+        <v>-1.8654</v>
       </c>
       <c r="G25" t="n">
         <v>-1.5021</v>
@@ -2404,13 +2404,13 @@
         <v>1.0995</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1562</v>
+        <v>-0.6827</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8808</v>
+        <v>-0.6885</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2754</v>
+        <v>0.0058</v>
       </c>
       <c r="V25" t="n">
         <v>-1.9005</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-15</v>
+        <v>-11.7949</v>
       </c>
       <c r="E26" t="n">
         <v>-10.8709</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.1291</v>
+        <v>-0.9238999999999997</v>
       </c>
       <c r="G26" t="n">
         <v>-12.4322</v>
@@ -2455,7 +2455,7 @@
         <v>-4.006799999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3175999999999999</v>
+        <v>-0.3176000000000008</v>
       </c>
       <c r="K26" t="n">
         <v>6.732200000000001</v>
@@ -2482,16 +2482,16 @@
         <v>11.9115</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7353999999999999</v>
+        <v>2.4698</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.5759</v>
+        <v>-1.5758</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8405999999999999</v>
+        <v>4.045799999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>-9.999999999932285e-05</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="W26" t="n">
         <v>4.7668</v>
